--- a/branches/dev/CodeSystem-mii-cs-onko-allgemeiner-leistungszustand-karnofsky.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-onko-allgemeiner-leistungszustand-karnofsky.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.0.3</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T02:28:56+00:00</t>
+    <t>2026-09-03T12:57:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-mii-cs-onko-allgemeiner-leistungszustand-karnofsky.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-onko-allgemeiner-leistungszustand-karnofsky.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T12:57:16+00:00</t>
+    <t>2026-09-03T15:50:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-mii-cs-onko-allgemeiner-leistungszustand-karnofsky.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-onko-allgemeiner-leistungszustand-karnofsky.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T15:50:39+00:00</t>
+    <t>2026-09-03T16:38:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-mii-cs-onko-allgemeiner-leistungszustand-karnofsky.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-onko-allgemeiner-leistungszustand-karnofsky.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T16:38:13+00:00</t>
+    <t>2026-09-03T19:21:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-mii-cs-onko-allgemeiner-leistungszustand-karnofsky.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-onko-allgemeiner-leistungszustand-karnofsky.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T19:21:23+00:00</t>
+    <t>2026-09-03T20:25:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-mii-cs-onko-allgemeiner-leistungszustand-karnofsky.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-onko-allgemeiner-leistungszustand-karnofsky.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T20:25:33+00:00</t>
+    <t>2026-09-04T14:14:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-mii-cs-onko-allgemeiner-leistungszustand-karnofsky.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-onko-allgemeiner-leistungszustand-karnofsky.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T14:14:24+00:00</t>
+    <t>2026-09-04T15:21:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-mii-cs-onko-allgemeiner-leistungszustand-karnofsky.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-onko-allgemeiner-leistungszustand-karnofsky.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T15:21:29+00:00</t>
+    <t>2026-09-04T16:20:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-mii-cs-onko-allgemeiner-leistungszustand-karnofsky.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-onko-allgemeiner-leistungszustand-karnofsky.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T16:20:32+00:00</t>
+    <t>2026-09-04T19:28:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-mii-cs-onko-allgemeiner-leistungszustand-karnofsky.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-onko-allgemeiner-leistungszustand-karnofsky.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T19:28:42+00:00</t>
+    <t>2026-09-05T05:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-mii-cs-onko-allgemeiner-leistungszustand-karnofsky.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-onko-allgemeiner-leistungszustand-karnofsky.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-05T05:33:13+00:00</t>
+    <t>2026-09-05T06:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-mii-cs-onko-allgemeiner-leistungszustand-karnofsky.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-onko-allgemeiner-leistungszustand-karnofsky.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-05T06:32:59+00:00</t>
+    <t>2026-09-05T07:29:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-mii-cs-onko-allgemeiner-leistungszustand-karnofsky.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-onko-allgemeiner-leistungszustand-karnofsky.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-05T07:29:05+00:00</t>
+    <t>2026-09-07T08:59:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-mii-cs-onko-allgemeiner-leistungszustand-karnofsky.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-onko-allgemeiner-leistungszustand-karnofsky.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T08:59:25+00:00</t>
+    <t>2026-09-08T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-mii-cs-onko-allgemeiner-leistungszustand-karnofsky.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-onko-allgemeiner-leistungszustand-karnofsky.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot.rc2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T11:16:16+00:00</t>
+    <t>2026-09-09T11:12:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-mii-cs-onko-allgemeiner-leistungszustand-karnofsky.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-onko-allgemeiner-leistungszustand-karnofsky.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T11:12:15+00:00</t>
+    <t>2026-09-09T13:30:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-mii-cs-onko-allgemeiner-leistungszustand-karnofsky.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-onko-allgemeiner-leistungszustand-karnofsky.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T13:30:31+00:00</t>
+    <t>2026-09-09T15:05:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
